--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487441_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487441_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9592</v>
+        <v>6.6826</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7052</v>
+        <v>5.3484</v>
       </c>
       <c r="F2" t="n">
-        <v>1.254</v>
+        <v>1.3342</v>
       </c>
       <c r="G2" t="n">
         <v>2.891</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>2.503</v>
+        <v>1.2264</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4784</v>
+        <v>1.1216</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0246</v>
+        <v>0.1048</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1767</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.53</v>
+        <v>4.2395</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4011</v>
+        <v>1.6027</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1289</v>
+        <v>2.6368</v>
       </c>
       <c r="G3" t="n">
         <v>1.2237</v>
@@ -688,13 +688,13 @@
         <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2588</v>
+        <v>0.4507</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7258</v>
+        <v>0.4758</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.533</v>
+        <v>-0.0251</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1767</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1833</v>
+        <v>2.3834</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2674</v>
+        <v>0.5744</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9159</v>
+        <v>1.809</v>
       </c>
       <c r="G4" t="n">
         <v>0.3958</v>
@@ -766,13 +766,13 @@
         <v>1.7626</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2016</v>
+        <v>0.4017</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0882</v>
+        <v>0.3952</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1134</v>
+        <v>0.0065</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1767</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2499</v>
+        <v>1.9555</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0513</v>
+        <v>1.1145</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3011</v>
+        <v>0.841</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6727</v>
+        <v>1.5474</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0413</v>
+        <v>1.9167</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6314</v>
+        <v>-0.3693</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.2769</v>
+        <v>0.9173</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6351</v>
+        <v>2.3886</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6418</v>
+        <v>-1.4713</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3958</v>
+        <v>0.6301</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4062</v>
+        <v>-0.4718</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0104</v>
+        <v>1.102</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S5" t="n">
-        <v>5.0021</v>
+        <v>0.4892</v>
       </c>
       <c r="T5" t="n">
-        <v>3.517</v>
+        <v>0.5681</v>
       </c>
       <c r="U5" t="n">
-        <v>1.485</v>
+        <v>-0.079</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8837</v>
+        <v>-1.0604</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3329</v>
+        <v>0.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5507</v>
+        <v>-1.6687</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7187</v>
+        <v>0.4193</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.034</v>
+        <v>-0.4567</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7527</v>
+        <v>0.8759</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9757</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2186</v>
+        <v>0.2191</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7571</v>
+        <v>-0.7731</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5915</v>
+        <v>-0.5602</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1228</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4687</v>
+        <v>-0.6418</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3842</v>
+        <v>0.0062</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0957</v>
+        <v>0.1375</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2885</v>
+        <v>-0.1313</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4485</v>
+        <v>0.1898</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0369</v>
+        <v>0.1035</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4116</v>
+        <v>0.0863</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3346</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.125</v>
+        <v>-0.4356</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5823</v>
+        <v>-0.7339</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7073</v>
+        <v>0.2983</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5474</v>
+        <v>2.9757</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9167</v>
+        <v>2.2186</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3693</v>
+        <v>0.7571</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9173</v>
+        <v>1.5915</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3886</v>
+        <v>1.1228</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4713</v>
+        <v>0.4687</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6301</v>
+        <v>1.3842</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4718</v>
+        <v>1.0957</v>
       </c>
       <c r="O7" t="n">
-        <v>1.102</v>
+        <v>0.2885</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9792</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3412</v>
+        <v>0.2942</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1286</v>
+        <v>0.337</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2126</v>
+        <v>-0.0428</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0604</v>
+        <v>-2.3346</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6687</v>
+        <v>-2.6099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.081</v>
+        <v>-1.0245</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6613</v>
+        <v>-2.791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7423</v>
+        <v>1.7665</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-2.6727</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2191</v>
+        <v>-2.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7731</v>
+        <v>-0.6314</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5602</v>
+        <v>-2.2769</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08169999999999999</v>
+        <v>-1.6351</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6418</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0062</v>
+        <v>-0.3958</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1375</v>
+        <v>-0.4062</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1313</v>
+        <v>0.0104</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1485</v>
+        <v>2.7278</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1012</v>
+        <v>1.7773</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0473</v>
+        <v>0.9504</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6008</v>
+        <v>-1.4744</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4875</v>
+        <v>-1.0933</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8866</v>
+        <v>-0.3811</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8290999999999999</v>
+        <v>1.5779</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8391</v>
+        <v>-0.9326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01</v>
+        <v>2.5106</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4104</v>
+        <v>2.105</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9714</v>
+        <v>-0.9358</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5610000000000001</v>
+        <v>3.0408</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4187</v>
+        <v>-0.5271</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1323</v>
+        <v>0.0031</v>
       </c>
       <c r="O9" t="n">
-        <v>0.551</v>
+        <v>-0.5302</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1751</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6852</v>
+        <v>-0.2689</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0963</v>
+        <v>-0.2605</v>
       </c>
       <c r="U9" t="n">
-        <v>0.589</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9401</v>
+        <v>-1.2166</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.0564</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8837</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3455</v>
+        <v>-1.5621</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7238</v>
+        <v>-3.128</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6217</v>
+        <v>1.5659</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5779</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9326</v>
+        <v>0.8391</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5106</v>
+        <v>-0.01</v>
       </c>
       <c r="J10" t="n">
-        <v>2.105</v>
+        <v>0.4104</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9358</v>
+        <v>0.9714</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0408</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5271</v>
+        <v>0.4187</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0031</v>
+        <v>-0.1323</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5302</v>
+        <v>0.551</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5668</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.14</v>
+        <v>0.724</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.891</v>
+        <v>0.4558</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.249</v>
+        <v>0.2682</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2166</v>
+        <v>-1.9401</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.0564</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6484</v>
+        <v>-3.0402</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.1637</v>
+        <v>-6.8762</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5153</v>
+        <v>3.836</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5266</v>
@@ -1312,13 +1312,13 @@
         <v>3.1336</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3177</v>
+        <v>0.2905</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9328</v>
+        <v>0.3546</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3849</v>
+        <v>-0.0641</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,28 +1345,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.252400000000001</v>
+        <v>8.143499999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3302</v>
+        <v>-6.439099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>14.5824</v>
+        <v>14.5825</v>
       </c>
       <c r="G12" t="n">
-        <v>4.687399999999998</v>
+        <v>4.6874</v>
       </c>
       <c r="H12" t="n">
         <v>8.176399999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.489</v>
+        <v>-3.488999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>3.151500000000001</v>
+        <v>3.1515</v>
       </c>
       <c r="K12" t="n">
-        <v>7.4525</v>
+        <v>7.452499999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-4.301</v>
@@ -1381,7 +1381,7 @@
         <v>0.8120999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>4.896199999999999</v>
+        <v>4.8962</v>
       </c>
       <c r="Q12" t="n">
         <v>-14.6885</v>
@@ -1390,10 +1390,10 @@
         <v>19.5848</v>
       </c>
       <c r="S12" t="n">
-        <v>5.634200000000001</v>
+        <v>6.525399999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>4.4374</v>
+        <v>5.3284</v>
       </c>
       <c r="U12" t="n">
         <v>1.1968</v>
@@ -1405,7 +1405,7 @@
         <v>-0.2302000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.735099999999999</v>
+        <v>-7.7351</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2358</v>
+        <v>3.0533</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6848</v>
+        <v>1.5824</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5511</v>
+        <v>1.4709</v>
       </c>
       <c r="G13" t="n">
         <v>1.3564</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2677</v>
+        <v>0.0851</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1059</v>
+        <v>0.0035</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1618</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>3.3745</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9419</v>
+        <v>2.2767</v>
       </c>
       <c r="E14" t="n">
-        <v>3.501</v>
+        <v>1.7074</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5592</v>
+        <v>0.5693</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0619</v>
+        <v>1.7064</v>
       </c>
       <c r="H14" t="n">
-        <v>0.231</v>
+        <v>-1.1282</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2929</v>
+        <v>2.8346</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9506</v>
+        <v>2.4179</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9101</v>
+        <v>0.0238</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0404</v>
+        <v>2.3941</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0124</v>
+        <v>-0.7115</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6791</v>
+        <v>-1.152</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3333</v>
+        <v>0.4405</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9792</v>
+        <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0257</v>
+        <v>-1.3881</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3339</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3082</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9988</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3926</v>
+        <v>1.3905</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0934</v>
+        <v>2.6824</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2992</v>
+        <v>-1.2918</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7064</v>
+        <v>-1.0619</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1282</v>
+        <v>0.231</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8346</v>
+        <v>-1.2929</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4179</v>
+        <v>0.9506</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0238</v>
+        <v>0.9101</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3941</v>
+        <v>0.0404</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7115</v>
+        <v>-2.0124</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.152</v>
+        <v>-0.6791</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4405</v>
+        <v>-1.3333</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1543</v>
+        <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2723</v>
+        <v>0.4743</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1286</v>
+        <v>0.5152</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1436</v>
+        <v>-0.0409</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.9988</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2178</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9636</v>
+        <v>1.3093</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1575</v>
+        <v>-1.0552</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1211</v>
+        <v>2.3645</v>
       </c>
       <c r="G16" t="n">
         <v>1.0237</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4714</v>
+        <v>-1.1257</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4576</v>
+        <v>-0.3552</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0138</v>
+        <v>-0.7705</v>
       </c>
       <c r="V16" t="n">
         <v>1.6071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1287</v>
+        <v>0.1941</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5028</v>
+        <v>-0.7075</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6315</v>
+        <v>0.9016</v>
       </c>
       <c r="G17" t="n">
         <v>-2.4001</v>
@@ -1780,13 +1780,13 @@
         <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4712</v>
+        <v>-1.4058</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.31</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1613</v>
+        <v>-0.8912</v>
       </c>
       <c r="V17" t="n">
         <v>2.4332</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2074</v>
+        <v>-2.0275</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.3393</v>
+        <v>-5.5206</v>
       </c>
       <c r="F18" t="n">
-        <v>4.1319</v>
+        <v>3.4932</v>
       </c>
       <c r="G18" t="n">
         <v>1.2111</v>
@@ -1858,13 +1858,13 @@
         <v>2.9377</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9532</v>
+        <v>-0.7732</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2298</v>
+        <v>-0.4111</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2766</v>
+        <v>-0.3621</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1152</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5456</v>
+        <v>-2.4165</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4833</v>
+        <v>-1.3809</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0623</v>
+        <v>-1.0356</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8363</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.101</v>
+        <v>0.0281</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.942</v>
+        <v>-5.013</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.3859</v>
+        <v>-5.5906</v>
       </c>
       <c r="F20" t="n">
-        <v>0.444</v>
+        <v>0.5776</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0927</v>
@@ -2014,13 +2014,13 @@
         <v>1.7626</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0297</v>
+        <v>-0.0413</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2952</v>
+        <v>0.0906</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2655</v>
+        <v>-0.1319</v>
       </c>
       <c r="V20" t="n">
         <v>0.2754</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.22</v>
+        <v>-5.3371</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9928</v>
+        <v>-6.2998</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7728</v>
+        <v>0.9628</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5939</v>
@@ -2092,13 +2092,13 @@
         <v>2.3502</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6884</v>
+        <v>-0.8055</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3129</v>
+        <v>0.0059</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0012</v>
+        <v>-0.8113</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.2524</v>
+        <v>-6.570200000000001</v>
       </c>
       <c r="E22" t="n">
         <v>-14.5824</v>
       </c>
       <c r="F22" t="n">
-        <v>7.3301</v>
+        <v>8.012499999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6873</v>
@@ -2140,7 +2140,7 @@
         <v>-8.176399999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4891</v>
+        <v>3.489100000000001</v>
       </c>
       <c r="J22" t="n">
         <v>-1.535799999999999</v>
@@ -2149,7 +2149,7 @@
         <v>-0.7238</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.8120000000000002</v>
       </c>
       <c r="M22" t="n">
         <v>-3.1515</v>
@@ -2158,7 +2158,7 @@
         <v>-7.452599999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>4.301100000000001</v>
+        <v>4.3011</v>
       </c>
       <c r="P22" t="n">
         <v>-4.896100000000001</v>
@@ -2170,13 +2170,13 @@
         <v>14.6885</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.634399999999999</v>
+        <v>-4.9521</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1969</v>
+        <v>-1.1968</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.4374</v>
+        <v>-3.7552</v>
       </c>
       <c r="V22" t="n">
         <v>7.965499999999999</v>
